--- a/python-excel-pca-demo.xlsx
+++ b/python-excel-pca-demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2000001_{86A3A04E-4D47-47F1-A717-8D4D9311A0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558A9433-BA10-4DD7-9F94-DE64FC7794DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -297,8 +297,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -353,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -365,6 +366,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -394,8 +401,8 @@
       <xdr:rowOff>127001</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>419101</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>152401</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>152049</xdr:rowOff>
     </xdr:to>
@@ -979,7 +986,14 @@
     <col min="2" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.5" bestFit="1" customWidth="1"/>
     <col min="8" max="11" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.44140625" style="7" customWidth="1"/>
+    <col min="15" max="15" width="13.71875" style="7" customWidth="1"/>
+    <col min="16" max="16" width="7.71875" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="5.83203125" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1016,7 +1030,7 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="e" cm="1" vm="1">
+      <c r="M1" s="7" t="e" cm="1" vm="1">
         <f t="array" ref="M1">_xlfn._xlws.PY(0,1,MonthlyReturns[#All])</f>
         <v>#VALUE!</v>
       </c>
@@ -1090,35 +1104,35 @@
       <c r="K3" s="3">
         <v>-1.9789999999999999E-2</v>
       </c>
-      <c r="M3" t="str" cm="1">
+      <c r="M3" s="7" t="str" cm="1">
         <f t="array" ref="M3:V8">_xlfn._xlws.PY(1,0)</f>
         <v>AAPL</v>
       </c>
-      <c r="N3" t="str">
+      <c r="N3" s="7" t="str">
         <v>MSFT</v>
       </c>
-      <c r="O3" t="str">
+      <c r="O3" s="7" t="str">
         <v>NVDA</v>
       </c>
-      <c r="P3" t="str">
+      <c r="P3" s="7" t="str">
         <v>AMZN</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="Q3" s="7" t="str">
         <v>META</v>
       </c>
-      <c r="R3" t="str">
+      <c r="R3" s="7" t="str">
         <v>GOOGL</v>
       </c>
-      <c r="S3" t="str">
+      <c r="S3" s="7" t="str">
         <v>NFLX</v>
       </c>
-      <c r="T3" t="str">
+      <c r="T3" s="7" t="str">
         <v>ORCL</v>
       </c>
-      <c r="U3" t="str">
+      <c r="U3" s="7" t="str">
         <v>CRM</v>
       </c>
-      <c r="V3" t="str">
+      <c r="V3" s="7" t="str">
         <v>ADBE</v>
       </c>
     </row>
@@ -1156,34 +1170,34 @@
       <c r="K4" s="3">
         <v>5.1599999999999997E-3</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="7">
         <v>4.5089999999999998E-2</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="7">
         <v>3.5450000000000002E-2</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="7">
         <v>-1.6500000000000001E-2</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="7">
         <v>-1.324E-2</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="7">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="7">
         <v>8.0189999999999997E-2</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="7">
         <v>7.9299999999999995E-3</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="7">
         <v>3.7600000000000001E-2</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="7">
         <v>4.5769999999999998E-2</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="7">
         <v>-1.6000000000000001E-3</v>
       </c>
     </row>
@@ -1221,34 +1235,34 @@
       <c r="K5" s="3">
         <v>2.3109999999999999E-2</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="7">
         <v>-2.682E-2</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="7">
         <v>-2.086E-2</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="7">
         <v>-6.7200000000000003E-3</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="7">
         <v>-2.2499999999999999E-2</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="7">
         <v>7.5870000000000007E-2</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="7">
         <v>5.2670000000000002E-2</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="7">
         <v>-5.91E-2</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="7">
         <v>-2.7449999999999999E-2</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="7">
         <v>-3.7990000000000003E-2</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="7">
         <v>-1.9789999999999999E-2</v>
       </c>
     </row>
@@ -1286,34 +1300,34 @@
       <c r="K6" s="3">
         <v>1.2E-4</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="7">
         <v>5.5030000000000003E-2</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="7">
         <v>-1.41E-2</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="7">
         <v>3.2370000000000003E-2</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="7">
         <v>3.952E-2</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="7">
         <v>1.14E-3</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="7">
         <v>1.89E-3</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="7">
         <v>-9.672E-2</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="7">
         <v>2.538E-2</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="7">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="7">
         <v>5.1599999999999997E-3</v>
       </c>
     </row>
@@ -1351,34 +1365,34 @@
       <c r="K7" s="3">
         <v>4.5109999999999997E-2</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="7">
         <v>7.2500000000000004E-3</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="7">
         <v>5.7860000000000002E-2</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="7">
         <v>9.5930000000000001E-2</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="7">
         <v>7.0129999999999998E-2</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="7">
         <v>6.5720000000000001E-2</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="7">
         <v>7.1360000000000007E-2</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="7">
         <v>4.7160000000000001E-2</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="7">
         <v>7.4829999999999994E-2</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="7">
         <v>8.9260000000000006E-2</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="7">
         <v>2.3109999999999999E-2</v>
       </c>
     </row>
@@ -1416,34 +1430,34 @@
       <c r="K8" s="3">
         <v>6.9400000000000003E-2</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="7">
         <v>3.78E-2</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="7">
         <v>1.2109999999999999E-2</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="7">
         <v>-2.7439999999999999E-2</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="7">
         <v>2.18E-2</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="7">
         <v>6.2080000000000003E-2</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="7">
         <v>3.95E-2</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="7">
         <v>-1.5429999999999999E-2</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="7">
         <v>-4.9099999999999998E-2</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="7">
         <v>4.1549999999999997E-2</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="7">
         <v>1.2E-4</v>
       </c>
     </row>
@@ -1516,7 +1530,7 @@
       <c r="K10" s="3">
         <v>-9.1590000000000005E-2</v>
       </c>
-      <c r="M10" t="e" cm="1" vm="2">
+      <c r="M10" s="7" t="e" cm="1" vm="2">
         <f t="array" ref="M10">_xlfn._xlws.PY(2,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -1556,7 +1570,7 @@
         <v>5.3719999999999997E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" ht="41">
       <c r="A12" s="2">
         <v>44501</v>
       </c>
@@ -1590,14 +1604,14 @@
       <c r="K12" s="3">
         <v>4.5060000000000003E-2</v>
       </c>
-      <c r="M12" t="str" cm="1">
+      <c r="M12" s="7" t="str" cm="1">
         <f t="array" ref="M12:O22">_xlfn._xlws.PY(3,0)</f>
         <v>Component</v>
       </c>
-      <c r="N12" t="str">
+      <c r="N12" s="7" t="str">
         <v>Explained Variance</v>
       </c>
-      <c r="O12" t="str">
+      <c r="O12" s="7" t="str">
         <v>Cumulative Variance</v>
       </c>
     </row>
@@ -1635,13 +1649,13 @@
       <c r="K13" s="3">
         <v>-3.5920000000000001E-2</v>
       </c>
-      <c r="M13" t="str">
+      <c r="M13" s="7" t="str">
         <v>PC1</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="7">
         <v>0.65976974434388913</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="7">
         <v>0.65976974434388913</v>
       </c>
     </row>
@@ -1679,13 +1693,13 @@
       <c r="K14" s="3">
         <v>8.5800000000000008E-3</v>
       </c>
-      <c r="M14" t="str">
+      <c r="M14" s="7" t="str">
         <v>PC2</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="7">
         <v>8.2669390325153899E-2</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="7">
         <v>0.74243913466904299</v>
       </c>
     </row>
@@ -1723,13 +1737,13 @@
       <c r="K15" s="3">
         <v>-3.925E-2</v>
       </c>
-      <c r="M15" t="str">
+      <c r="M15" s="7" t="str">
         <v>PC3</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="7">
         <v>7.0252885633523846E-2</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="7">
         <v>0.81269202030256682</v>
       </c>
     </row>
@@ -1767,13 +1781,13 @@
       <c r="K16" s="3">
         <v>-0.19275</v>
       </c>
-      <c r="M16" t="str">
+      <c r="M16" s="7" t="str">
         <v>PC4</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="7">
         <v>5.8116940708416671E-2</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="7">
         <v>0.87080896101098348</v>
       </c>
     </row>
@@ -1811,13 +1825,13 @@
       <c r="K17" s="3">
         <v>-1.6310000000000002E-2</v>
       </c>
-      <c r="M17" t="str">
+      <c r="M17" s="7" t="str">
         <v>PC5</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="7">
         <v>3.397517931587437E-2</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="7">
         <v>0.90478414032685783</v>
       </c>
     </row>
@@ -1855,13 +1869,13 @@
       <c r="K18" s="3">
         <v>-6.9819999999999993E-2</v>
       </c>
-      <c r="M18" t="str">
+      <c r="M18" s="7" t="str">
         <v>PC6</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="7">
         <v>2.9933465125758958E-2</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="7">
         <v>0.93471760545261684</v>
       </c>
     </row>
@@ -1899,13 +1913,13 @@
       <c r="K19" s="3">
         <v>7.7189999999999995E-2</v>
       </c>
-      <c r="M19" t="str">
+      <c r="M19" s="7" t="str">
         <v>PC7</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="7">
         <v>2.2942006752109268E-2</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="7">
         <v>0.95765961220472606</v>
       </c>
     </row>
@@ -1943,13 +1957,13 @@
       <c r="K20" s="3">
         <v>6.5500000000000003E-3</v>
       </c>
-      <c r="M20" t="str">
+      <c r="M20" s="7" t="str">
         <v>PC8</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="7">
         <v>1.8486013254736131E-2</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="7">
         <v>0.97614562545946215</v>
       </c>
     </row>
@@ -1987,13 +2001,13 @@
       <c r="K21" s="3">
         <v>-6.6259999999999999E-2</v>
       </c>
-      <c r="M21" t="str">
+      <c r="M21" s="7" t="str">
         <v>PC9</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="7">
         <v>1.348002131685353E-2</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="7">
         <v>0.9896256467763157</v>
       </c>
     </row>
@@ -2031,13 +2045,13 @@
       <c r="K22" s="3">
         <v>9.4159999999999994E-2</v>
       </c>
-      <c r="M22" t="str">
+      <c r="M22" s="7" t="str">
         <v>PC10</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="7">
         <v>1.0374353223684043E-2</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="7">
         <v>0.99999999999999978</v>
       </c>
     </row>
@@ -2110,7 +2124,7 @@
       <c r="K24" s="3">
         <v>3.9949999999999999E-2</v>
       </c>
-      <c r="M24" t="e" cm="1" vm="3">
+      <c r="M24" s="7" t="e" cm="1" vm="3">
         <f t="array" ref="M24">_xlfn._xlws.PY(4,0)</f>
         <v>#VALUE!</v>
       </c>
@@ -2849,14 +2863,14 @@
       <c r="K45" s="3">
         <v>-7.5609999999999997E-2</v>
       </c>
-      <c r="M45" t="str" cm="1">
+      <c r="M45" s="7" t="str" cm="1">
         <f t="array" ref="M45:O50">_xlfn._xlws.PY(5,0)</f>
         <v>PC1</v>
       </c>
-      <c r="N45" t="str">
+      <c r="N45" s="7" t="str">
         <v>PC2</v>
       </c>
-      <c r="O45" t="str">
+      <c r="O45" s="7" t="str">
         <v>PC3</v>
       </c>
     </row>
@@ -2894,13 +2908,13 @@
       <c r="K46" s="3">
         <v>-0.11337999999999999</v>
       </c>
-      <c r="M46">
+      <c r="M46" s="7">
         <v>6.9407608190289405E-2</v>
       </c>
-      <c r="N46">
+      <c r="N46" s="7">
         <v>-3.3466883176403041E-2</v>
       </c>
-      <c r="O46">
+      <c r="O46" s="7">
         <v>-1.5865373325221852E-3</v>
       </c>
     </row>
@@ -2938,13 +2952,13 @@
       <c r="K47" s="3">
         <v>1.2659999999999999E-2</v>
       </c>
-      <c r="M47">
+      <c r="M47" s="7">
         <v>-3.6829660551438444E-2</v>
       </c>
-      <c r="N47">
+      <c r="N47" s="7">
         <v>2.2427194525448065E-2</v>
       </c>
-      <c r="O47">
+      <c r="O47" s="7">
         <v>-8.7847095855160012E-2</v>
       </c>
     </row>
@@ -2982,13 +2996,13 @@
       <c r="K48" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="M48">
+      <c r="M48" s="7">
         <v>1.2935060031162187E-2</v>
       </c>
-      <c r="N48">
+      <c r="N48" s="7">
         <v>-2.5532741672465734E-2</v>
       </c>
-      <c r="O48">
+      <c r="O48" s="7">
         <v>-5.6186385267088843E-2</v>
       </c>
     </row>
@@ -3026,13 +3040,13 @@
       <c r="K49" s="3">
         <v>0.12417</v>
       </c>
-      <c r="M49">
+      <c r="M49" s="7">
         <v>0.17644134267608283</v>
       </c>
-      <c r="N49">
+      <c r="N49" s="7">
         <v>9.7548423223831737E-3</v>
       </c>
-      <c r="O49">
+      <c r="O49" s="7">
         <v>9.5473077504437866E-3</v>
       </c>
     </row>
@@ -3070,13 +3084,13 @@
       <c r="K50" s="3">
         <v>-3.9019999999999999E-2</v>
       </c>
-      <c r="M50">
+      <c r="M50" s="7">
         <v>2.8607511606480999E-2</v>
       </c>
-      <c r="N50">
+      <c r="N50" s="7">
         <v>-3.786645662483281E-2</v>
       </c>
-      <c r="O50">
+      <c r="O50" s="7">
         <v>-2.5768256876468956E-2</v>
       </c>
     </row>
@@ -3184,17 +3198,17 @@
       <c r="K53" s="3">
         <v>-1.0120000000000001E-2</v>
       </c>
-      <c r="M53" t="str" cm="1">
+      <c r="M53" s="7" t="str" cm="1">
         <f t="array" ref="M53:P58">_xlfn._xlws.PY(6,0)</f>
         <v>Date</v>
       </c>
-      <c r="N53" t="str">
+      <c r="N53" s="7" t="str">
         <v>PC1</v>
       </c>
-      <c r="O53" t="str">
+      <c r="O53" s="7" t="str">
         <v>PC2</v>
       </c>
-      <c r="P53" t="str">
+      <c r="P53" s="7" t="str">
         <v>PC3</v>
       </c>
     </row>
@@ -3232,16 +3246,16 @@
       <c r="K54" s="3">
         <v>-3.6049999999999999E-2</v>
       </c>
-      <c r="M54" vm="4">
+      <c r="M54" s="8" vm="4">
         <v>44197</v>
       </c>
-      <c r="N54">
+      <c r="N54" s="7">
         <v>6.9407608190289405E-2</v>
       </c>
-      <c r="O54">
+      <c r="O54" s="7">
         <v>-3.3466883176403041E-2</v>
       </c>
-      <c r="P54">
+      <c r="P54" s="7">
         <v>-1.5865373325221852E-3</v>
       </c>
     </row>
@@ -3279,16 +3293,16 @@
       <c r="K55" s="3">
         <v>0.12578</v>
       </c>
-      <c r="M55" vm="5">
+      <c r="M55" s="8" vm="5">
         <v>44228</v>
       </c>
-      <c r="N55">
+      <c r="N55" s="7">
         <v>-3.6829660551438444E-2</v>
       </c>
-      <c r="O55">
+      <c r="O55" s="7">
         <v>2.2427194525448065E-2</v>
       </c>
-      <c r="P55">
+      <c r="P55" s="7">
         <v>-8.7847095855160012E-2</v>
       </c>
     </row>
@@ -3326,16 +3340,16 @@
       <c r="K56" s="3">
         <v>4.9279999999999997E-2</v>
       </c>
-      <c r="M56" vm="6">
+      <c r="M56" s="8" vm="6">
         <v>44256</v>
       </c>
-      <c r="N56">
+      <c r="N56" s="7">
         <v>1.2935060031162187E-2</v>
       </c>
-      <c r="O56">
+      <c r="O56" s="7">
         <v>-2.5532741672465734E-2</v>
       </c>
-      <c r="P56">
+      <c r="P56" s="7">
         <v>-5.6186385267088843E-2</v>
       </c>
     </row>
@@ -3373,16 +3387,16 @@
       <c r="K57" s="3">
         <v>9.9640000000000006E-2</v>
       </c>
-      <c r="M57" vm="7">
+      <c r="M57" s="8" vm="7">
         <v>44287</v>
       </c>
-      <c r="N57">
+      <c r="N57" s="7">
         <v>0.17644134267608283</v>
       </c>
-      <c r="O57">
+      <c r="O57" s="7">
         <v>9.7548423223831737E-3</v>
       </c>
-      <c r="P57">
+      <c r="P57" s="7">
         <v>9.5473077504437866E-3</v>
       </c>
     </row>
@@ -3420,16 +3434,16 @@
       <c r="K58" s="3">
         <v>-2.2970000000000001E-2</v>
       </c>
-      <c r="M58" vm="8">
+      <c r="M58" s="8" vm="8">
         <v>44317</v>
       </c>
-      <c r="N58">
+      <c r="N58" s="7">
         <v>2.8607511606480999E-2</v>
       </c>
-      <c r="O58">
+      <c r="O58" s="7">
         <v>-3.786645662483281E-2</v>
       </c>
-      <c r="P58">
+      <c r="P58" s="7">
         <v>-2.5768256876468956E-2</v>
       </c>
     </row>
@@ -3502,26 +3516,26 @@
       <c r="K60" s="3">
         <v>4.7129999999999998E-2</v>
       </c>
-      <c r="M60" t="str" cm="1">
+      <c r="M60" s="7" t="str" cm="1">
         <f t="array" ref="M60:S64">_xlfn._xlws.PY(7,0)</f>
         <v/>
       </c>
-      <c r="N60" t="str">
+      <c r="N60" s="7" t="str">
         <v>coef</v>
       </c>
-      <c r="O60" t="str">
+      <c r="O60" s="7" t="str">
         <v>std err</v>
       </c>
-      <c r="P60" t="str">
+      <c r="P60" s="7" t="str">
         <v>t</v>
       </c>
-      <c r="Q60" t="str">
+      <c r="Q60" s="7" t="str">
         <v>P&gt;|t|</v>
       </c>
-      <c r="R60" t="str">
+      <c r="R60" s="7" t="str">
         <v>[0.025</v>
       </c>
-      <c r="S60" t="str">
+      <c r="S60" s="7" t="str">
         <v>0.975]</v>
       </c>
     </row>
@@ -3559,94 +3573,94 @@
       <c r="K61" s="3">
         <v>7.4490000000000001E-2</v>
       </c>
-      <c r="M61" t="str">
+      <c r="M61" s="7" t="str">
         <v>const</v>
       </c>
-      <c r="N61" t="str">
+      <c r="N61" s="7" t="str">
         <v xml:space="preserve">    0.0069</v>
       </c>
-      <c r="O61" t="str">
+      <c r="O61" s="7" t="str">
         <v xml:space="preserve">    0.004</v>
       </c>
-      <c r="P61" t="str">
+      <c r="P61" s="7" t="str">
         <v xml:space="preserve">    1.863</v>
       </c>
-      <c r="Q61" t="str">
+      <c r="Q61" s="7" t="str">
         <v xml:space="preserve"> 0.068</v>
       </c>
-      <c r="R61" t="str">
+      <c r="R61" s="7" t="str">
         <v xml:space="preserve">   -0.001</v>
       </c>
-      <c r="S61" t="str">
+      <c r="S61" s="7" t="str">
         <v xml:space="preserve">    0.014</v>
       </c>
     </row>
     <row r="62" spans="1:19">
-      <c r="M62" t="str">
+      <c r="M62" s="7" t="str">
         <v>PC1</v>
       </c>
-      <c r="N62" t="str">
+      <c r="N62" s="7" t="str">
         <v xml:space="preserve">    0.3359</v>
       </c>
-      <c r="O62" t="str">
+      <c r="O62" s="7" t="str">
         <v xml:space="preserve">    0.023</v>
       </c>
-      <c r="P62" t="str">
+      <c r="P62" s="7" t="str">
         <v xml:space="preserve">   14.641</v>
       </c>
-      <c r="Q62" t="str">
+      <c r="Q62" s="7" t="str">
         <v xml:space="preserve"> 0.000</v>
       </c>
-      <c r="R62" t="str">
+      <c r="R62" s="7" t="str">
         <v xml:space="preserve">    0.290</v>
       </c>
-      <c r="S62" t="str">
+      <c r="S62" s="7" t="str">
         <v xml:space="preserve">    0.382</v>
       </c>
     </row>
     <row r="63" spans="1:19">
-      <c r="M63" t="str">
+      <c r="M63" s="7" t="str">
         <v>PC2</v>
       </c>
-      <c r="N63" t="str">
+      <c r="N63" s="7" t="str">
         <v xml:space="preserve">   -0.0358</v>
       </c>
-      <c r="O63" t="str">
+      <c r="O63" s="7" t="str">
         <v xml:space="preserve">    0.065</v>
       </c>
-      <c r="P63" t="str">
+      <c r="P63" s="7" t="str">
         <v xml:space="preserve">   -0.552</v>
       </c>
-      <c r="Q63" t="str">
+      <c r="Q63" s="7" t="str">
         <v xml:space="preserve"> 0.583</v>
       </c>
-      <c r="R63" t="str">
+      <c r="R63" s="7" t="str">
         <v xml:space="preserve">   -0.166</v>
       </c>
-      <c r="S63" t="str">
+      <c r="S63" s="7" t="str">
         <v xml:space="preserve">    0.094</v>
       </c>
     </row>
     <row r="64" spans="1:19">
-      <c r="M64" t="str">
+      <c r="M64" s="7" t="str">
         <v>PC3</v>
       </c>
-      <c r="N64" t="str">
+      <c r="N64" s="7" t="str">
         <v xml:space="preserve">   -0.0035</v>
       </c>
-      <c r="O64" t="str">
+      <c r="O64" s="7" t="str">
         <v xml:space="preserve">    0.070</v>
       </c>
-      <c r="P64" t="str">
+      <c r="P64" s="7" t="str">
         <v xml:space="preserve">   -0.050</v>
       </c>
-      <c r="Q64" t="str">
+      <c r="Q64" s="7" t="str">
         <v xml:space="preserve"> 0.960</v>
       </c>
-      <c r="R64" t="str">
+      <c r="R64" s="7" t="str">
         <v xml:space="preserve">   -0.144</v>
       </c>
-      <c r="S64" t="str">
+      <c r="S64" s="7" t="str">
         <v xml:space="preserve">    0.137</v>
       </c>
     </row>

--- a/python-excel-pca-demo.xlsx
+++ b/python-excel-pca-demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558A9433-BA10-4DD7-9F94-DE64FC7794DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267F1F17-FC6F-4FA1-B4CD-79EC0C183AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -143,7 +143,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization>
+    <initialization userModified="1">
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -401,8 +401,8 @@
       <xdr:rowOff>127001</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>152401</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>406401</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>152049</xdr:rowOff>
     </xdr:to>
@@ -987,8 +987,8 @@
     <col min="7" max="7" width="7.5" bestFit="1" customWidth="1"/>
     <col min="8" max="11" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.44140625" style="7" customWidth="1"/>
-    <col min="15" max="15" width="13.71875" style="7" customWidth="1"/>
+    <col min="14" max="14" width="8.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.71875" style="7" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5.83203125" style="7" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.5" style="7" bestFit="1" customWidth="1"/>
@@ -1570,7 +1570,7 @@
         <v>5.3719999999999997E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="41">
+    <row r="12" spans="1:22" ht="27.35">
       <c r="A12" s="2">
         <v>44501</v>
       </c>

--- a/python-excel-pca-demo.xlsx
+++ b/python-excel-pca-demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267F1F17-FC6F-4FA1-B4CD-79EC0C183AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CFFB4B3-430A-43B7-821F-009356118EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
